--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488039_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488039_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1609</v>
+        <v>3.3187</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1995</v>
+        <v>3.3187</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0386</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5835</v>
+        <v>3.3187</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2304</v>
+        <v>0.908</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3531</v>
+        <v>2.4107</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7411</v>
+        <v>3.3187</v>
       </c>
       <c r="K2" t="n">
-        <v>4.009</v>
+        <v>0.908</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7321</v>
+        <v>2.4107</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1576</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2214</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.379</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>5.844</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.967</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.877</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.8879</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.5509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3187</v>
+        <v>2.5286</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3187</v>
+        <v>5.4095</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-2.8809</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3187</v>
+        <v>6.5835</v>
       </c>
       <c r="H3" t="n">
-        <v>0.908</v>
+        <v>4.2304</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4107</v>
+        <v>2.3531</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3187</v>
+        <v>6.7411</v>
       </c>
       <c r="K3" t="n">
-        <v>0.908</v>
+        <v>4.009</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4107</v>
+        <v>2.7321</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.1576</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.2214</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.379</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.2117</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.177</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.0346</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-3.8879</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-3.5509</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3174</v>
+        <v>1.9214</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2622</v>
+        <v>0.6697</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0552</v>
+        <v>1.2517</v>
       </c>
       <c r="G4" t="n">
         <v>1.3222</v>
@@ -766,13 +766,13 @@
         <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5995</v>
+        <v>0.0046</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4257</v>
+        <v>-0.0183</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1737</v>
+        <v>0.0228</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0805</v>
+        <v>-0.8487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.604</v>
+        <v>0.8077</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6845</v>
+        <v>-1.6565</v>
       </c>
       <c r="G5" t="n">
         <v>1.3817</v>
@@ -844,13 +844,13 @@
         <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6604</v>
+        <v>-0.4286</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2236</v>
+        <v>-0.1956</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2071</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9593</v>
+        <v>-1.6152</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5054</v>
+        <v>-0.3016</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4539</v>
+        <v>-1.3135</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3848</v>
@@ -922,13 +922,13 @@
         <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9709</v>
+        <v>-0.6268</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5966</v>
+        <v>-0.4562</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0258</v>
+        <v>-1.6193</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.379</v>
+        <v>-1.1128</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6468</v>
+        <v>-0.5064</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2195</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4276</v>
+        <v>-0.0211</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.312</v>
+        <v>-0.0459</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1157</v>
+        <v>0.0247</v>
       </c>
       <c r="V7" t="n">
         <v>1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6063</v>
+        <v>-2.0065</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2992</v>
+        <v>-0.7275</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3071</v>
+        <v>-1.279</v>
       </c>
       <c r="G8" t="n">
         <v>0.8300999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.921</v>
+        <v>-0.3212</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8736</v>
+        <v>-0.3018</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0475</v>
+        <v>-0.0194</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5331</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6384</v>
+        <v>-2.5542</v>
       </c>
       <c r="E9" t="n">
         <v>-0.904</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7344</v>
+        <v>-1.6501</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2277</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5385</v>
+        <v>-0.4543</v>
       </c>
       <c r="T9" t="n">
         <v>0.0148</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5533</v>
+        <v>-0.4691</v>
       </c>
       <c r="V9" t="n">
         <v>-0.674</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARCIA GAZQUEZ</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3168</v>
+        <v>-3.3881</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6137</v>
+        <v>-0.7178</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-2.6703</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4724</v>
+        <v>-0.4063</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7254</v>
+        <v>0.3991</v>
       </c>
       <c r="I10" t="n">
-        <v>1.253</v>
+        <v>-0.8054</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6004</v>
+        <v>0.0832</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.2962</v>
+        <v>0.1078</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6958</v>
+        <v>-0.0246</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.872</v>
+        <v>-0.4895</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5708</v>
+        <v>0.2913</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4428</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9733</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.1627</v>
+        <v>-1.1893</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3182</v>
+        <v>-0.1028</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0721</v>
+        <v>0.3883</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7539</v>
+        <v>-0.4912</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8107</v>
+        <v>-2.6808</v>
       </c>
       <c r="W10" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>D. GARCIA GAZQUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1646</v>
+        <v>-3.5424</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6346</v>
+        <v>-2.7551</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5299</v>
+        <v>-0.7874</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4063</v>
+        <v>-2.4724</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3991</v>
+        <v>-3.7254</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8054</v>
+        <v>1.253</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0832</v>
+        <v>-1.6004</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1078</v>
+        <v>-4.2962</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0246</v>
+        <v>2.6958</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4895</v>
+        <v>-0.872</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2913</v>
+        <v>0.5708</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.4428</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1893</v>
+        <v>-4.1627</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8792</v>
+        <v>0.0926</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5285</v>
+        <v>0.9308</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3508</v>
+        <v>-0.8381</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6808</v>
+        <v>1.8107</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6808</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4239</v>
+        <v>-4.3968</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2298</v>
+        <v>-2.3712</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1941</v>
+        <v>-2.0257</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6406</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3869</v>
+        <v>-0.3597</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4847</v>
+        <v>0.3434</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8716</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0423</v>
+        <v>-4.9466</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2087</v>
+        <v>-4.3937</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8336</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3861</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2004</v>
+        <v>-0.1046</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4661</v>
+        <v>0.3489</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7343</v>
+        <v>-0.4535</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8701</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.4609</v>
+        <v>-17.1491</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.390000000000001</v>
+        <v>-3.0781</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.0708</v>
+        <v>-14.071</v>
       </c>
       <c r="G14" t="n">
         <v>0.6988000000000003</v>
       </c>
       <c r="H14" t="n">
-        <v>1.378000000000001</v>
+        <v>1.378</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6791999999999998</v>
+        <v>-0.6792000000000007</v>
       </c>
       <c r="J14" t="n">
         <v>10.0461</v>
@@ -1546,16 +1546,16 @@
         <v>7.928800000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4221999999999992</v>
+        <v>-0.1101999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1215</v>
+        <v>3.4336</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.544</v>
+        <v>-3.5441</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.835200000000001</v>
+        <v>-6.8352</v>
       </c>
       <c r="W14" t="n">
         <v>2.2733</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.347799999999999</v>
+        <v>6.5367</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9945</v>
+        <v>6.2982</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3533</v>
+        <v>0.2385</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.035</v>
+        <v>2.3964</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1442</v>
+        <v>0.7854</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1792</v>
+        <v>1.611</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7402</v>
+        <v>4.3704</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2565</v>
+        <v>1.3052</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9967</v>
+        <v>3.0652</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2948</v>
+        <v>-1.9739</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1123</v>
+        <v>-0.5198</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1825</v>
+        <v>-1.4542</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5769</v>
+        <v>1.3876</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>3.568</v>
+        <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5809</v>
+        <v>0.1423</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8379</v>
+        <v>0.3085</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7431</v>
+        <v>-0.1662</v>
       </c>
       <c r="V15" t="n">
-        <v>4.2249</v>
+        <v>2.6104</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8879</v>
+        <v>2.6104</v>
       </c>
       <c r="X15" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4177</v>
+        <v>6.3985</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9749</v>
+        <v>3.4664</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4428</v>
+        <v>2.9321</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4883</v>
+        <v>-2.035</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6728</v>
+        <v>0.1442</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8155</v>
+        <v>-2.1792</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9079</v>
+        <v>-0.7402</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8549</v>
+        <v>0.2565</v>
       </c>
       <c r="L16" t="n">
-        <v>2.053</v>
+        <v>-0.9967</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4196</v>
+        <v>-1.2948</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1822</v>
+        <v>-0.1123</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2374</v>
+        <v>-1.1825</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1893</v>
+        <v>2.5769</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1805</v>
+        <v>3.568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7996</v>
+        <v>1.6317</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7916</v>
+        <v>1.3098</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.992</v>
+        <v>0.3219</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9405</v>
+        <v>4.2249</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2666</v>
+        <v>3.8879</v>
       </c>
       <c r="X16" t="n">
-        <v>0.674</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3567</v>
+        <v>5.3368</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4832</v>
+        <v>3.2618</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1265</v>
+        <v>2.0749</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3964</v>
+        <v>2.4883</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7854</v>
+        <v>0.6728</v>
       </c>
       <c r="I17" t="n">
-        <v>1.611</v>
+        <v>1.8155</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3704</v>
+        <v>2.9079</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3052</v>
+        <v>0.8549</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0652</v>
+        <v>2.053</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9739</v>
+        <v>-0.4196</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5198</v>
+        <v>-0.1822</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4542</v>
+        <v>-0.2374</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0377</v>
+        <v>0.7186</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5064</v>
+        <v>1.0785</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5313</v>
+        <v>-0.3599</v>
       </c>
       <c r="V17" t="n">
-        <v>2.6104</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6104</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5806</v>
+        <v>3.406</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2912</v>
+        <v>2.5968</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2894</v>
+        <v>0.8092</v>
       </c>
       <c r="G18" t="n">
         <v>3.9794</v>
@@ -1858,13 +1858,13 @@
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.718</v>
+        <v>0.1074</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>0.1846</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.597</v>
+        <v>-0.0772</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4737</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0882</v>
+        <v>2.3178</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0535</v>
+        <v>2.0722</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0347</v>
+        <v>0.2456</v>
       </c>
       <c r="G19" t="n">
         <v>0.8631</v>
@@ -1936,13 +1936,13 @@
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4379</v>
+        <v>-0.2083</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9873</v>
+        <v>0.0314</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4506</v>
+        <v>-0.2397</v>
       </c>
       <c r="V19" t="n">
         <v>0.8701</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0567</v>
+        <v>0.7158</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4972</v>
+        <v>0.5804</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4405</v>
+        <v>0.1354</v>
       </c>
       <c r="G20" t="n">
         <v>-1.298</v>
@@ -2014,13 +2014,13 @@
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="T20" t="n">
-        <v>1.351</v>
+        <v>0.4342</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7981</v>
+        <v>-0.2222</v>
       </c>
       <c r="V20" t="n">
         <v>1.2071</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.534</v>
+        <v>0.0599</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1377</v>
+        <v>-0.1679</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3963</v>
+        <v>0.2279</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1309</v>
@@ -2092,13 +2092,13 @@
         <v>2.3787</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8898</v>
+        <v>0.4158</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5471</v>
+        <v>0.2415</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3427</v>
+        <v>0.1743</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6036</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. MATEO HINOJO</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.444</v>
+        <v>0.0136</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0422</v>
+        <v>-1.1132</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4018</v>
+        <v>1.1268</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2458</v>
+        <v>-1.2708</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0202</v>
+        <v>-2.1127</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.266</v>
+        <v>0.8419</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0202</v>
+        <v>0.4297</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>-1.9965</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.4262</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.266</v>
+        <v>-1.7005</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1162</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.266</v>
+        <v>-1.5843</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1982</v>
+        <v>0.0266</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0624</v>
+        <v>0.1727</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1358</v>
+        <v>-0.1461</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>P. MATEO HINOJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2126</v>
+        <v>-0.444</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.0422</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.449</v>
+        <v>-0.4018</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9707</v>
+        <v>-0.2458</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1614</v>
+        <v>0.0202</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8093</v>
+        <v>-0.266</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6388</v>
+        <v>0.0202</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0404</v>
+        <v>0.0202</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3319</v>
+        <v>-0.266</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2018</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1301</v>
+        <v>-0.266</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2419</v>
+        <v>-0.1982</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1248</v>
+        <v>-0.0624</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1171</v>
+        <v>-0.1358</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2931</v>
+        <v>-0.9264</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3356</v>
+        <v>-1.6231</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0425</v>
+        <v>0.6967</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2708</v>
+        <v>-0.5189</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1127</v>
+        <v>0.0226</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8419</v>
+        <v>-0.5415</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4297</v>
+        <v>-0.4779</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9965</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>2.4262</v>
+        <v>-0.5586</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7005</v>
+        <v>-0.041</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1162</v>
+        <v>-0.0581</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5843</v>
+        <v>0.0171</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9733</v>
+        <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.28</v>
+        <v>-0.2093</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0497</v>
+        <v>-0.1541</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2303</v>
+        <v>-0.0552</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5167</v>
+        <v>-1.0826</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0306</v>
+        <v>-0.6617</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5139</v>
+        <v>-0.4209</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5189</v>
+        <v>-0.9707</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0226</v>
+        <v>-0.1614</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5415</v>
+        <v>-0.8093</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4779</v>
+        <v>-0.6388</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5586</v>
+        <v>-0.6791</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.041</v>
+        <v>-0.3319</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0581</v>
+        <v>-0.2018</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0171</v>
+        <v>-0.1301</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7996</v>
+        <v>-0.112</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5616</v>
+        <v>-0.0229</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.238</v>
+        <v>-0.089</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4542</v>
+        <v>-2.8336</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1892</v>
+        <v>-0.5967</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.265</v>
+        <v>-2.2369</v>
       </c>
       <c r="G26" t="n">
         <v>-1.956</v>
@@ -2482,13 +2482,13 @@
         <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3124</v>
+        <v>-0.067</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4295</v>
+        <v>0.0221</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2071</v>
@@ -2515,31 +2515,31 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>17.4611</v>
+        <v>19.4985</v>
       </c>
       <c r="E27" t="n">
         <v>14.071</v>
       </c>
       <c r="F27" t="n">
-        <v>3.390099999999999</v>
+        <v>5.4275</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6988999999999996</v>
+        <v>-0.6988999999999992</v>
       </c>
       <c r="H27" t="n">
         <v>-1.3779</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6790000000000003</v>
+        <v>0.6789999999999998</v>
       </c>
       <c r="J27" t="n">
-        <v>9.347300000000001</v>
+        <v>9.347300000000002</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8322999999999998</v>
+        <v>0.8323</v>
       </c>
       <c r="L27" t="n">
-        <v>8.5152</v>
+        <v>8.515199999999998</v>
       </c>
       <c r="M27" t="n">
         <v>-10.0461</v>
@@ -2548,7 +2548,7 @@
         <v>-2.2104</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.835999999999999</v>
+        <v>-7.836</v>
       </c>
       <c r="P27" t="n">
         <v>10.9023</v>
@@ -2560,16 +2560,16 @@
         <v>18.8312</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4223000000000007</v>
+        <v>2.4596</v>
       </c>
       <c r="T27" t="n">
-        <v>3.543900000000001</v>
+        <v>3.5439</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.1215</v>
+        <v>-1.0841</v>
       </c>
       <c r="V27" t="n">
-        <v>6.835199999999999</v>
+        <v>6.8352</v>
       </c>
       <c r="W27" t="n">
         <v>9.108700000000001</v>
